--- a/results/result1.xlsx
+++ b/results/result1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="计划购电量" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="充放电量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>

--- a/results/result1.xlsx
+++ b/results/result1.xlsx
@@ -1959,11 +1959,16 @@
           <t>0:00-4:00</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>4499.999999999999</v>
+      </c>
       <c r="C2" t="n">
-        <v>4499.999999999999</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>6000</v>
@@ -1975,11 +1980,16 @@
           <t>4:00-8:00</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>833.3333333333333</v>
+      </c>
       <c r="C3" t="n">
-        <v>833.3333333333333</v>
-      </c>
-      <c r="D3" s="6" t="n">
         <v>6365.8412</v>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
       </c>
       <c r="E3" t="n">
         <v>6000</v>
@@ -1991,10 +2001,10 @@
           <t>8:00-12:00</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>4787.964288065848</v>
+      </c>
       <c r="C4" t="n">
-        <v>4787.964288065848</v>
-      </c>
-      <c r="D4" t="n">
         <v>1702.996983333333</v>
       </c>
     </row>
@@ -2004,10 +2014,10 @@
           <t>12:00-16:00</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>5286.035176954732</v>
+      </c>
       <c r="C5" t="n">
-        <v>5286.035176954732</v>
-      </c>
-      <c r="D5" t="n">
         <v>91.10138333333344</v>
       </c>
     </row>
@@ -2017,10 +2027,10 @@
           <t>16:00-20:00</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
         <v>5780.131883333333</v>
       </c>
     </row>
@@ -2030,10 +2040,10 @@
           <t>20:00-24:00</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>5333.333333333332</v>
+      </c>
       <c r="C7" t="n">
-        <v>5333.333333333332</v>
-      </c>
-      <c r="D7" t="n">
         <v>2859.868116666667</v>
       </c>
     </row>
